--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532227.8030347079</v>
+        <v>532228</v>
       </c>
       <c r="R4" t="n">
-        <v>6907304.773005469</v>
+        <v>6907305</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,19 +976,9 @@
           <t>2020-07-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,11 +920,6 @@
       </c>
       <c r="E4" t="n">
         <v>219790</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,6 +920,11 @@
       </c>
       <c r="E4" t="n">
         <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2023 artfynd.xlsx
+++ b/artfynd/A 52131-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>89123101</v>
       </c>
       <c r="B4" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
